--- a/server/excel/release/hero-summon.xlsx
+++ b/server/excel/release/hero-summon.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="英雄召唤" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="英雄召唤星组" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="英雄召唤作弊" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sheet(基础召唤概率)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sheet(友情召唤概率)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Sheet(高级召唤概率)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Sheet(积分召唤概率)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="英雄召唤" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="英雄召唤星组" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="英雄召唤作弊" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet(基础召唤概率)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet(友情召唤概率)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet(高级召唤概率)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet(积分召唤概率)" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">修正</t>
   </si>
   <si>
-    <t xml:space="preserve">Phổ Công</t>
+    <t xml:space="preserve">Đánh thường</t>
   </si>
   <si>
     <t xml:space="preserve">Y Sư</t>
